--- a/sampleprojects/CorporateTax/excel/states/IL_corp.xlsx
+++ b/sampleprojects/CorporateTax/excel/states/IL_corp.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="96">
   <si>
     <t>DT: Determine IL Filing Requirement</t>
   </si>
@@ -149,7 +149,7 @@
     <t>Calculate IL tax at 9.5% flat rate; Calculate IL state tax, apply credits, and calculate refund/owed</t>
   </si>
   <si>
-    <t>set apportionment.state_tax = apportionment.state_taxable_income * apportionment.state_tax_rate; set apportionment.state_tax = the maximum of (0.0) and (apportionment.state_tax - apportionment.state_credits); set apportionment.state_refund_or_owed = apportionment.state_payments - apportionment.state_tax; add "IL state corporate income tax calculation: 1. Federal taxable income: [Form 1120 line 28], 2. Apportioned to IL: x [Apportionment %], 3. State additions: + [Additions], 4. State subtractions: - [Subtractions], 5. IL taxable income: = [Result], 6. IL tax rate: x 9.5% (highest in the nation), 7. IL income tax: = [Tax before credits], 8. IL credits: - [Credits], 9. IL tax liability (before replacement tax): = [Tax]. Note: Personal Property Replacement Tax (2.5%) calculated separately. Total effective IL corporate tax rate is 12.0% (9.5% + 2.5%). Reference: IL Form IL-1120 Instructions, 35 ILCS 5/201(b) (Tax rate: 9.5%), 35 ILCS 5/201(c) (Replacement tax: 2.5%), 86 Ill. Admin. Code § 100.2250 (Computation of tax)" to result.policy_statements;</t>
+    <t>set apportionment.state_tax = apportionment.state_taxable_income * il_apportionment.state_tax_rate; set apportionment.state_tax = the maximum of (0.0) and (apportionment.state_tax - apportionment.state_credits); set apportionment.state_refund_or_owed = apportionment.state_payments - apportionment.state_tax; add "IL state corporate income tax calculation: 1. Federal taxable income: [Form 1120 line 28], 2. Apportioned to IL: x [Apportionment %], 3. State additions: + [Additions], 4. State subtractions: - [Subtractions], 5. IL taxable income: = [Result], 6. IL tax rate: x 9.5% (highest in the nation), 7. IL income tax: = [Tax before credits], 8. IL credits: - [Credits], 9. IL tax liability (before replacement tax): = [Tax]. Note: Personal Property Replacement Tax (2.5%) calculated separately. Total effective IL corporate tax rate is 12.0% (9.5% + 2.5%). Reference: IL Form IL-1120 Instructions, 35 ILCS 5/201(b) (Tax rate: 9.5%), 35 ILCS 5/201(c) (Replacement tax: 2.5%), 86 Ill. Admin. Code § 100.2250 (Computation of tax)" to result.policy_statements;</t>
   </si>
   <si>
     <t>No IL nexus - no tax liability</t>
@@ -176,13 +176,13 @@
     <t>Calculate replacement tax at 2.5%; Calculate replacement tax, add to total state tax, recalculate refund/owed</t>
   </si>
   <si>
-    <t>set result.il_replacement_tax = apportionment.state_taxable_income * result.il_replacement_tax_rate; set apportionment.state_tax = apportionment.state_tax + result.il_replacement_tax; set apportionment.state_refund_or_owed = apportionment.state_payments - apportionment.state_tax; add "IL Personal Property Replacement Tax (PPRT) applies to corporations. Replacement Tax Calculation: Net income base: [State taxable income], Replacement tax rate: x 2.5%, Replacement tax: = [Replacement tax amount], Total IL tax: Income tax (9.5%) + Replacement tax (2.5%) = 12.0%. The replacement tax applies to the same income base as the income tax. It was enacted to replace revenue lost when the personal property tax on corporations was abolished by the 1970 Illinois Constitution. The replacement tax revenue is distributed to local governments to replace the lost personal property tax revenue. Reference: 35 ILCS 5/201(c) (Replacement tax rate: 2.5%), 35 ILCS 5/201(d) (Replacement tax base), IL Form IL-1120 Instructions (Schedule of Replacement Tax), 86 Ill. Admin. Code § 100.2260 (Personal Property Replacement Tax)" to result.policy_statements;</t>
+    <t>set il_result.replacement_tax = apportionment.state_taxable_income * il_result.replacement_tax_rate; set apportionment.state_tax = apportionment.state_tax + il_result.replacement_tax; set apportionment.state_refund_or_owed = apportionment.state_payments - apportionment.state_tax; add "IL Personal Property Replacement Tax (PPRT) applies to corporations. Replacement Tax Calculation: Net income base: [State taxable income], Replacement tax rate: x 2.5%, Replacement tax: = [Replacement tax amount], Total IL tax: Income tax (9.5%) + Replacement tax (2.5%) = 12.0%. The replacement tax applies to the same income base as the income tax. It was enacted to replace revenue lost when the personal property tax on corporations was abolished by the 1970 Illinois Constitution. The replacement tax revenue is distributed to local governments to replace the lost personal property tax revenue. Reference: 35 ILCS 5/201(c) (Replacement tax rate: 2.5%), 35 ILCS 5/201(d) (Replacement tax base), IL Form IL-1120 Instructions (Schedule of Replacement Tax), 86 Ill. Admin. Code § 100.2260 (Personal Property Replacement Tax)" to result.policy_statements;</t>
   </si>
   <si>
     <t>No replacement tax - no IL nexus</t>
   </si>
   <si>
-    <t>set result.il_replacement_tax = 0.0;</t>
+    <t>set il_result.replacement_tax = 0.0;</t>
   </si>
   <si>
     <t>No replacement tax - no positive tax base</t>
@@ -230,10 +230,10 @@
     <t>Reference</t>
   </si>
   <si>
-    <t>apportionment</t>
-  </si>
-  <si>
-    <t>(8 attributes)</t>
+    <t>il_apportionment</t>
+  </si>
+  <si>
+    <t>(4 attributes)</t>
   </si>
   <si>
     <t>apportionment_formula</t>
@@ -263,70 +263,43 @@
     <t>Economic nexus gross receipts threshold - IL uses $100K threshold</t>
   </si>
   <si>
-    <t>state_additions</t>
+    <t>state_tax_rate</t>
+  </si>
+  <si>
+    <t>0.095</t>
+  </si>
+  <si>
+    <t>IL corporate income tax rate - 9.5% per 35 ILCS 5/201 (highest in nation)</t>
+  </si>
+  <si>
+    <t>transaction_threshold</t>
+  </si>
+  <si>
+    <t>integer</t>
+  </si>
+  <si>
+    <t>200</t>
+  </si>
+  <si>
+    <t>Economic nexus transaction count threshold - Default 200</t>
+  </si>
+  <si>
+    <t>il_result</t>
+  </si>
+  <si>
+    <t>(2 attributes)</t>
+  </si>
+  <si>
+    <t>replacement_tax</t>
   </si>
   <si>
     <t>0.0</t>
   </si>
   <si>
-    <t>State-specific additions: federal interest, IRC 199A addback, bonus depreciation, etc.</t>
-  </si>
-  <si>
-    <t>state_code</t>
-  </si>
-  <si>
-    <t>IL</t>
-  </si>
-  <si>
-    <t>Two-letter state code - Illinois</t>
-  </si>
-  <si>
-    <t>state_credits</t>
-  </si>
-  <si>
-    <t>State tax credits: R&amp;D, jobs, film, renewable energy, etc.</t>
-  </si>
-  <si>
-    <t>state_subtractions</t>
-  </si>
-  <si>
-    <t>State-specific subtractions: municipal interest, state taxes, state NOL, etc.</t>
-  </si>
-  <si>
-    <t>state_tax_rate</t>
-  </si>
-  <si>
-    <t>0.095</t>
-  </si>
-  <si>
-    <t>IL corporate income tax rate - 9.5% per 35 ILCS 5/201 (highest in nation)</t>
-  </si>
-  <si>
-    <t>transaction_threshold</t>
-  </si>
-  <si>
-    <t>integer</t>
-  </si>
-  <si>
-    <t>200</t>
-  </si>
-  <si>
-    <t>Economic nexus transaction count threshold - Default 200</t>
-  </si>
-  <si>
-    <t>result</t>
-  </si>
-  <si>
-    <t>(2 attributes)</t>
-  </si>
-  <si>
-    <t>il_replacement_tax</t>
-  </si>
-  <si>
     <t>IL personal property replacement tax amount calculated</t>
   </si>
   <si>
-    <t>il_replacement_tax_rate</t>
+    <t>replacement_tax_rate</t>
   </si>
   <si>
     <t>0.025</t>
@@ -3176,14 +3149,14 @@
       <c r="B7" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="C7" s="10" t="s">
-        <v>73</v>
+      <c r="C7" s="11" t="s">
+        <v>85</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>14</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F7" s="8" t="s">
         <v>14</v>
@@ -3192,7 +3165,7 @@
         <v>75</v>
       </c>
       <c r="H7" s="16" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I7" s="8" t="s">
         <v>14</v>
@@ -3211,267 +3184,103 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="C8" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="H8" s="16" t="s">
+      <c r="A8" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="I8" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="J8" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="K8" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="L8" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="M8" s="7" t="s">
-        <v>14</v>
-      </c>
+      <c r="B8" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C8" s="6"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="6"/>
+      <c r="I8" s="6"/>
+      <c r="J8" s="6"/>
+      <c r="K8" s="6"/>
+      <c r="L8" s="6"/>
+      <c r="M8" s="6"/>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="7" t="s">
         <v>14</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C9" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="D9" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="F9" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="G9" s="8" t="s">
+      <c r="D9" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G9" s="7" t="s">
         <v>75</v>
       </c>
       <c r="H9" s="16" t="s">
-        <v>90</v>
-      </c>
-      <c r="I9" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="J9" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K9" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="L9" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="M9" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="I9" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="J9" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K9" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="L9" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="M9" s="7" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="8" t="s">
         <v>14</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C10" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="D10" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G10" s="7" t="s">
+      <c r="D10" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G10" s="8" t="s">
         <v>75</v>
       </c>
       <c r="H10" s="16" t="s">
-        <v>93</v>
-      </c>
-      <c r="I10" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="J10" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="K10" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="L10" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="M10" s="7" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B11" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="C11" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="D11" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="F11" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="G11" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="H11" s="16" t="s">
-        <v>97</v>
-      </c>
-      <c r="I11" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="J11" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K11" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="L11" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="M11" s="8" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="6"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="6"/>
-      <c r="I12" s="6"/>
-      <c r="J12" s="6"/>
-      <c r="K12" s="6"/>
-      <c r="L12" s="6"/>
-      <c r="M12" s="6"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B13" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="C13" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="F13" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G13" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="H13" s="16" t="s">
-        <v>101</v>
-      </c>
-      <c r="I13" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="J13" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="K13" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="L13" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="M13" s="7" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B14" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="C14" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="D14" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E14" s="8" t="s">
-        <v>103</v>
-      </c>
-      <c r="F14" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="G14" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="H14" s="16" t="s">
-        <v>104</v>
-      </c>
-      <c r="I14" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="J14" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K14" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="L14" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="M14" s="8" t="s">
+      <c r="I10" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="J10" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="K10" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="L10" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="M10" s="8" t="s">
         <v>14</v>
       </c>
     </row>
